--- a/1_Data/Sui_2015_unpub/Codebook_Sui_2015_unpub_Exp1_Clean.xlsx
+++ b/1_Data/Sui_2015_unpub/Codebook_Sui_2015_unpub_Exp1_Clean.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="52" uniqueCount="52">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="54" uniqueCount="54">
   <si>
     <t xml:space="preserve">Variable_name</t>
   </si>
@@ -168,6 +168,12 @@
   </si>
   <si>
     <t xml:space="preserve">1;0;3;4</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Accuracy: 1 (correct); 0 (incorrect); -4 (response after the 1000 ms deadline; author raw code 3); NA (no response; author raw code 4)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1 (correct); 0 (incorrect); -4 (response after the 1000 ms deadline); NA (no response)</t>
   </si>
 </sst>
 </file>
@@ -767,10 +773,10 @@
         <v>49</v>
       </c>
       <c r="B20" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="C20" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="D20" t="s">
         <v>11</v>
